--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260904.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260904.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>10,500,000</t>
+          <t>10,300,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.99%</t>
+          <t>15.47%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>7.01%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.84%</t>
+          <t>5.80%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.40%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.98%</t>
+          <t>4.75%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>4.08%</t>
         </is>
       </c>
     </row>
@@ -748,51 +748,51 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>4.05%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>810,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>736,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -997,61 +997,61 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>4,500,000</t>
+          <t>3,400,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>3,400,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>4,500,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1166,249 +1166,249 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -1430,161 +1430,161 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,100,000</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,351,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>191,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1635,34 +1635,34 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,39 +1701,35 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>9,260,398,206</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>7,639,160,269</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1741,17 +1737,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>RDI_NTD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,171,153,518</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1759,38 +1755,20 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>RDI_NTD</t>
+          <t>RP_NTD</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>744,685,392</t>
+          <t>2,720,182,758</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>RP_NTD</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>RP</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>3,426,046,480</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
